--- a/out/C01_chronic_care_patient_journey/agent3/agent3_test_cases_for_review.xlsx
+++ b/out/C01_chronic_care_patient_journey/agent3/agent3_test_cases_for_review.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:K157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>TC-d321095528</t>
+          <t>TC-11d872a0c9</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Prove Q5 ACCEPTS an answer that obeys its rule. The QRE's rule is: “None of these” cannot be chosen alongside anything else</t>
+          <t>Prove Q5 REJECTS an answer that breaks its rule. The QRE's rule is: “None of these” cannot be chosen alongside anything else</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2720,12 +2720,13 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>At Q5, tick 1 option (None of these), then submit.</t>
+          <t>At Q5, tick 2 options (None of these, Primary-care physician), then submit.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2761,12 +2762,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>TC-178c64a1d5</t>
+          <t>TC-07168a0971</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Prove reject rule R19 does NOT fire. The rule is: exclusive option selected with another response at Q1 or Q5</t>
+          <t xml:space="preserve">Prove reject rule R19 DOES fire. The rule is: </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2788,7 +2789,8 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against R19</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2824,12 +2826,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>TC-11d872a0c9</t>
+          <t>TC-6a49619e2a</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Prove Q5 REJECTS an answer that breaks its rule. The QRE's rule is: “None of these” cannot be chosen alongside anything else</t>
+          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2846,7 +2848,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>At Q5, tick 2 options (None of these, Primary-care physician), then submit.</t>
+          <t>At Q5, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2857,7 +2859,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Answer rule accepts or rejects</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2888,12 +2890,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>TC-b0729c4af8</t>
+          <t>TC-5e6784210d</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Prove reject rule R19 DOES fire. The rule is: exclusive option selected with another response at Q1 or Q5</t>
+          <t>Prove Q5 still shows all 7 of its options when shuffled, with none dropped and none duplicated</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2902,23 +2904,26 @@
 2. S2 = Personally manage an ongoing chronic health condition
 3. S3 = No
 4. S4 = No
-5. Q1 = Care Network A + None of these</t>
+5. Q1 = Care Network A
+6. Q2 = Care Network A
+7. Q3 = Care Network A
+8. Q4 = Recently diagnosed</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>After submitting Q1, look for Q5 on the next page. Do not answer it.</t>
+          <t>At Q5, tick 1 option (Primary-care physician), then submit.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against R19</t>
+          <t>1. Q5 shows exactly 7 options, none missing and none repeated
+2. the options shown at Q5 are exactly: Hospital, None of these, Patient portal, Pharmacy, Primary-care physician, Specialist, Support programme</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Answer rule accepts or rejects</t>
+          <t>Shuffled options</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2949,17 +2954,18 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>TC-6a49619e2a</t>
+          <t>TC-ccad697776</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question</t>
+          <t>Prove Q5 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1. S1 = Yes
+          <t>Run this same path 5 times and record the option order each time, then compare them.
+1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
 3. S3 = No
 4. S4 = No
@@ -2971,18 +2977,17 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>At Q5, select nothing at all, then submit.</t>
+          <t>At Q5, tick 1 option (Primary-care physician), then submit.</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q5</t>
+          <t>1. the order the options appear in at Q5 is NOT identical on every run</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Blank answer is blocked</t>
+          <t>Shuffled options</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2997,159 +3002,31 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Q5 | Which touchpoints did you use? | multi | Primary-care physician; Specialist; Hospital; Pharmacy; Patient portal; Support programme; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>TC-5e6784210d</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q5 still shows all 7 of its options when shuffled, with none dropped and none duplicated</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>At Q5, tick 1 option (Primary-care physician), then submit.</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>1. Q5 shows exactly 7 options, none missing and none repeated
-2. the options shown at Q5 are exactly: Hospital, None of these, Patient portal, Pharmacy, Primary-care physician, Specialist, Support programme</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Shuffled options</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Q5 | Which touchpoints did you use? | multi | Primary-care physician; Specialist; Hospital; Pharmacy; Patient portal; Support programme; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>TC-ccad697776</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q5 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Run this same path 5 times and record the option order each time, then compare them.
-1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>At Q5, tick 1 option (Primary-care physician), then submit.</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>1. the order the options appear in at Q5 is NOT identical on every run</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Shuffled options</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Q6 | Which touchpoint was most influential? | single | Primary-care physician; Specialist; Hospital; Pharmacy; Patient portal; Support programme | Show if: Q5 contains any touchpoint
 Show only touchpoints selected at Q5.</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>TC-18b8ce728c</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q6: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -3181,20 +3058,149 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>1. Q6 IS shown on the page
 2. the next question shown is Q7</t>
         </is>
       </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Q6 | Which touchpoint was most influential? | single | Primary-care physician; Specialist; Hospital; Pharmacy; Patient portal; Support programme | Show if: Q5 contains any touchpoint
+Show only touchpoints selected at Q5.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>TC-b11bdf8ea9</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Prove reject rule R20 does NOT fire. The rule is: selected option at Q6 was not selected at Q5</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Personally manage an ongoing chronic health condition
+3. S3 = No
+4. S4 = No
+5. Q1 = Care Network A
+6. Q2 = Care Network A
+7. Q3 = Care Network A
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>At Q6, choose “Primary-care physician”, then submit.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Q6 | Which touchpoint was most influential? | single | Primary-care physician; Specialist; Hospital; Pharmacy; Patient portal; Support programme | Show if: Q5 contains any touchpoint
+Show only touchpoints selected at Q5.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>TC-8258786a5d</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Prove reject rule R20 DOES fire. The rule is: selected option at Q6 was not selected at Q5</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Personally manage an ongoing chronic health condition
+3. S3 = No
+4. S4 = No
+5. Q1 = Care Network A
+6. Q2 = Care Network A
+7. Q3 = Care Network A
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>At Q6, choose “Specialist”, then submit.</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against R20</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3225,12 +3231,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>TC-b11bdf8ea9</t>
+          <t>TC-ba8edd2da2</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Prove reject rule R20 does NOT fire. The rule is: selected option at Q6 was not selected at Q5</t>
+          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3248,17 +3254,18 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>At Q6, choose “Primary-care physician”, then submit.</t>
+          <t>At Q6, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Answer rule accepts or rejects</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3289,12 +3296,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>TC-8258786a5d</t>
+          <t>TC-58cba0a522</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Prove reject rule R20 DOES fire. The rule is: selected option at Q6 was not selected at Q5</t>
+          <t>Q6's option list comes from Q5's answer: the option list should be narrowed</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3312,18 +3319,17 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>At Q6, choose “Specialist”, then submit.</t>
+          <t>At Q6, choose “Primary-care physician”, then submit.</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against R20</t>
+          <t>1. Q6 offers exactly these options and no others: A001</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Answer rule accepts or rejects</t>
+          <t>Options carried forward</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3338,13 +3344,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Q6 | Which touchpoint was most influential? | single | Primary-care physician; Specialist; Hospital; Pharmacy; Patient portal; Support programme | Show if: Q5 contains any touchpoint
-Show only touchpoints selected at Q5.</t>
+          <t>Q7 | How satisfied are you with the overall experience? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3354,143 +3359,15 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>TC-ba8edd2da2</t>
+          <t>TC-d037ec05b3</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
+          <t>Prove the survey flows correctly at Q7: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>At Q6, select nothing at all, then submit.</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Blank answer is blocked</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Q6 | Which touchpoint was most influential? | single | Primary-care physician; Specialist; Hospital; Pharmacy; Patient portal; Support programme | Show if: Q5 contains any touchpoint
-Show only touchpoints selected at Q5.</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>TC-58cba0a522</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>Q6's option list comes from Q5's answer: the option list should be narrowed</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>At Q6, choose “Primary-care physician”, then submit.</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>1. Q6 offers exactly these options and no others: A001</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Options carried forward</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Q7 | How satisfied are you with the overall experience? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>TC-d037ec05b3</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey flows correctly at Q7: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -3522,15 +3399,144 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>1. Q7 IS shown on the page
 2. the next question shown is Q8</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Q7 | How satisfied are you with the overall experience? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>TC-4e8f85244a</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q7 DOES appear when its condition is met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Personally manage an ongoing chronic health condition
+3. S3 = No
+4. S4 = No
+5. Q1 = Care Network A
+6. Q2 = Care Network A
+7. Q3 = Care Network A
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician
+10. Q6 = Primary-care physician</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>At Q7, choose “Very poor”, then submit.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>1. Q7 IS shown on the page</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Q7 | How satisfied are you with the overall experience? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>TC-6e6caf4ac9</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q7 does NOT appear when its condition is not met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Personally manage an ongoing chronic health condition
+3. S3 = No
+4. S4 = No
+5. Q1 = Care Network A
+6. Q2 = Care Network A
+7. Q3 = None/currently not using
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician
+10. Q6 = Primary-care physician</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>After submitting Q6, look for Q7 on the next page. Do not answer it.</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>1. Q7 is NOT shown on the page
+2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3565,12 +3571,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>TC-4e8f85244a</t>
+          <t>TC-d5504b61ac</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Prove Q7 DOES appear when its condition is met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3589,17 +3595,18 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>At Q7, choose “Very poor”, then submit.</t>
+          <t>At Q7, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>1. Q7 IS shown on the page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q7</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3614,12 +3621,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Q7 | How satisfied are you with the overall experience? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'</t>
+          <t>Q8 | How likely are you to recommend the current provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3629,145 +3636,15 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>TC-6e6caf4ac9</t>
+          <t>TC-3fc25fff77</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Prove Q7 does NOT appear when its condition is not met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+          <t>Prove the survey flows correctly at Q8: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = None/currently not using
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician
-10. Q6 = Primary-care physician</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>After submitting Q6, look for Q7 on the next page. Do not answer it.</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>1. Q7 is NOT shown on the page
-2. the respondent carries on into the survey rather than being screened out or finished</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Q7 | How satisfied are you with the overall experience? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>TC-d5504b61ac</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician
-10. Q6 = Primary-care physician</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>At Q7, select nothing at all, then submit.</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q7</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Blank answer is blocked</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Q8 | How likely are you to recommend the current provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Show if: Q3 != 'None/currently not using'</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>TC-3fc25fff77</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey flows correctly at Q8: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -3799,15 +3676,145 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>1. Q8 IS shown on the page
 2. the next question shown is Q9_&lt;row&gt;</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Q8 | How likely are you to recommend the current provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Show if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>TC-8e12ac85c3</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q8 DOES appear when its condition is met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Personally manage an ongoing chronic health condition
+3. S3 = No
+4. S4 = No
+5. Q1 = Care Network A
+6. Q2 = Care Network A
+7. Q3 = Care Network A
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician
+10. Q6 = Primary-care physician
+11. Q7 = Very poor</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>At Q8, choose “0”, then submit.</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>1. Q8 IS shown on the page</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Q8 | How likely are you to recommend the current provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Show if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>TC-cccb5a3db3</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q8 does NOT appear when its condition is not met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Personally manage an ongoing chronic health condition
+3. S3 = No
+4. S4 = No
+5. Q1 = Care Network A
+6. Q2 = Care Network A
+7. Q3 = None/currently not using
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician
+10. Q6 = Primary-care physician</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>After submitting Q6, look for Q8 on the next page. Do not answer it.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>1. Q8 is NOT shown on the page
+2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3842,12 +3849,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>TC-8e12ac85c3</t>
+          <t>TC-134f7d8b2a</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Prove Q8 DOES appear when its condition is met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+          <t>Prove Q8 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -3867,17 +3874,18 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>At Q8, choose “0”, then submit.</t>
+          <t>At Q8, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>1. Q8 IS shown on the page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q8</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3907,12 +3915,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>TC-cccb5a3db3</t>
+          <t>TC-9c5ae726b5</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Prove Q8 does NOT appear when its condition is not met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+          <t>Q8's wording comes from Q3's answer: the earlier answer should appear in the wording</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3923,26 +3931,26 @@
 4. S4 = No
 5. Q1 = Care Network A
 6. Q2 = Care Network A
-7. Q3 = None/currently not using
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician
-10. Q6 = Primary-care physician</t>
+7. Q3 = Care Network A
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician
+10. Q6 = Primary-care physician
+11. Q7 = Very poor</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>After submitting Q6, look for Q8 on the next page. Do not answer it.</t>
+          <t>At Q8, choose “0”, then submit.</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>1. Q8 is NOT shown on the page
-2. the respondent carries on into the survey rather than being screened out or finished</t>
+          <t>1. Q8's wording includes the words: Care Network A</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Wording carried forward</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3972,12 +3980,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>TC-134f7d8b2a</t>
+          <t>TC-069d6e168f</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Prove Q8 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
+          <t>Q8 shown by its condition while also depending on Q3: both should hold at once</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -3997,18 +4005,18 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>At Q8, select nothing at all, then submit.</t>
+          <t>At Q8, choose “0”, then submit.</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q8</t>
+          <t>1. Q8 IS shown on the page
+2. Q8's wording includes the words: Care Network A</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Blank answer is blocked</t>
+          <t>Two behaviours together</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4023,163 +4031,32 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Q8 | How likely are you to recommend the current provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Show if: Q3 != 'None/currently not using'</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>TC-9c5ae726b5</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>Q8's wording comes from Q3's answer: the earlier answer should appear in the wording</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician
-10. Q6 = Primary-care physician
-11. Q7 = Very poor</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>At Q8, choose “0”, then submit.</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>1. Q8's wording includes the words: Care Network A</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Wording carried forward</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Q8 | How likely are you to recommend the current provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Show if: Q3 != 'None/currently not using'</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>TC-069d6e168f</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>Q8 shown by its condition while also depending on Q3: both should hold at once</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician
-10. Q6 = Primary-care physician
-11. Q7 = Very poor</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>At Q8, choose “0”, then submit.</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>1. Q8 IS shown on the page
-2. Q8's wording includes the words: Care Network A</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Two behaviours together</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Q9 | Please rate each attribute for your current provider. | matrix | Rows: Access; Communication; Coordination; Treatment information; Emotional support; Digital tools
 Scale: 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'
 Validate: {"scale": [</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>TC-4af41885da</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q9: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -4211,15 +4088,150 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>1. Q9 IS shown on the page
 2. the next question shown is Q10</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Q9 | Please rate each attribute for your current provider. | matrix | Rows: Access; Communication; Coordination; Treatment information; Emotional support; Digital tools
+Scale: 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'
+Validate: {"scale": [</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>TC-19e0284103</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q9 DOES appear when its condition is met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Personally manage an ongoing chronic health condition
+3. S3 = No
+4. S4 = No
+5. Q1 = Care Network A
+6. Q2 = Care Network A
+7. Q3 = Care Network A
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician
+10. Q6 = Primary-care physician
+11. Q7 = Very poor
+12. Q8 = 0</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>At Q9, fill in every row, then submit.</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>1. Q9 IS shown on the page</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Shows / hides correctly</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Q9 | Please rate each attribute for your current provider. | matrix | Rows: Access; Communication; Coordination; Treatment information; Emotional support; Digital tools
+Scale: 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'
+Validate: {"scale": [</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>TC-6fac2285dd</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q9 does NOT appear when its condition is not met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Personally manage an ongoing chronic health condition
+3. S3 = No
+4. S4 = No
+5. Q1 = Care Network A
+6. Q2 = Care Network A
+7. Q3 = None/currently not using
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician
+10. Q6 = Primary-care physician</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>After submitting Q6, look for Q9 on the next page. Do not answer it.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>1. Q9 is NOT shown on the page
+2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -4256,12 +4268,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>TC-19e0284103</t>
+          <t>TC-aba25e4bdc</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Prove Q9 DOES appear when its condition is met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+          <t>Prove Q9 ACCEPTS an answer that obeys its rule. The QRE's rule is: every row must be answered</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4287,12 +4299,12 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>1. Q9 IS shown on the page</t>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4324,12 +4336,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>TC-6fac2285dd</t>
+          <t>TC-93b2d25c27</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Prove Q9 does NOT appear when its condition is not met. The QRE says show it if: Q3 != 'None/currently not using'</t>
+          <t>Prove Q9 REJECTS an answer that breaks its rule. The QRE's rule is: every row must be answered</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4340,26 +4352,28 @@
 4. S4 = No
 5. Q1 = Care Network A
 6. Q2 = Care Network A
-7. Q3 = None/currently not using
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician
-10. Q6 = Primary-care physician</t>
+7. Q3 = Care Network A
+8. Q4 = Recently diagnosed
+9. Q5 = Primary-care physician
+10. Q6 = Primary-care physician
+11. Q7 = Very poor
+12. Q8 = 0</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>After submitting Q6, look for Q9 on the next page. Do not answer it.</t>
+          <t>At Q9, fill in every row, then submit.</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>1. Q9 is NOT shown on the page
-2. the respondent carries on into the survey rather than being screened out or finished</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q9</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Shows / hides correctly</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4391,12 +4405,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>TC-aba25e4bdc</t>
+          <t>TC-7958bf08f7</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Prove Q9 ACCEPTS an answer that obeys its rule. The QRE's rule is: every row must be answered</t>
+          <t>Prove Q9 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a matrix question</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4417,17 +4431,18 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>At Q9, fill in every row, then submit.</t>
+          <t>At Q9, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q9</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Answer rule accepts or rejects</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4459,12 +4474,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>TC-93b2d25c27</t>
+          <t>TC-ab65b6f0c0</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Prove Q9 REJECTS an answer that breaks its rule. The QRE's rule is: every row must be answered</t>
+          <t>Q9's wording comes from Q3's answer: the earlier answer should appear in the wording</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4490,13 +4505,12 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q9</t>
+          <t>1. Q9's wording includes the words: Care Network A</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Answer rule accepts or rejects</t>
+          <t>Wording carried forward</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4528,12 +4542,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>TC-7958bf08f7</t>
+          <t>TC-9980db1104</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Prove Q9 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a matrix question</t>
+          <t>Q9 shown by its condition while also depending on Q3: both should hold at once</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4554,18 +4568,18 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>At Q9, select nothing at all, then submit.</t>
+          <t>At Q9, fill in every row, then submit.</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q9</t>
+          <t>1. Q9 IS shown on the page
+2. Q9's wording includes the words: Care Network A</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Blank answer is blocked</t>
+          <t>Two behaviours together</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4597,12 +4611,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>TC-ab65b6f0c0</t>
+          <t>TC-f5050da245</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Q9's wording comes from Q3's answer: the earlier answer should appear in the wording</t>
+          <t>Prove Q9 still shows all 5 of its options when shuffled, with none dropped and none duplicated</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4628,12 +4642,13 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>1. Q9's wording includes the words: Care Network A</t>
+          <t>1. Q9 shows exactly 5 options, none missing and none repeated
+2. the options shown at Q9 are exactly: Excellent, Fair, Good, Poor, Very poor</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Wording carried forward</t>
+          <t>Shuffled options</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4665,17 +4680,18 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>TC-9980db1104</t>
+          <t>TC-39acc3e870</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Q9 shown by its condition while also depending on Q3: both should hold at once</t>
+          <t>Prove Q9 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1. S1 = Yes
+          <t>Run this same path 5 times and record the option order each time, then compare them.
+1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
 3. S3 = No
 4. S4 = No
@@ -4696,13 +4712,12 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>1. Q9 IS shown on the page
-2. Q9's wording includes the words: Care Network A</t>
+          <t>1. the order the options appear in at Q9 is NOT identical on every run</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Two behaviours together</t>
+          <t>Shuffled options</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4717,14 +4732,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Q9 | Please rate each attribute for your current provider. | matrix | Rows: Access; Communication; Coordination; Treatment information; Emotional support; Digital tools
-Scale: 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'
-Validate: {"scale": [</t>
+          <t>Q10 | Did you contact support during the experience? | single | Yes; No | Always show</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4734,151 +4747,15 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>TC-f5050da245</t>
+          <t>TC-a8e061598c</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Prove Q9 still shows all 5 of its options when shuffled, with none dropped and none duplicated</t>
+          <t>Prove the survey flows correctly at Q10: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician
-10. Q6 = Primary-care physician
-11. Q7 = Very poor
-12. Q8 = 0</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>At Q9, fill in every row, then submit.</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>1. Q9 shows exactly 5 options, none missing and none repeated
-2. the options shown at Q9 are exactly: Excellent, Fair, Good, Poor, Very poor</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>Shuffled options</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Q9 | Please rate each attribute for your current provider. | matrix | Rows: Access; Communication; Coordination; Treatment information; Emotional support; Digital tools
-Scale: 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q3 != 'None/currently not using'
-Validate: {"scale": [</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>TC-39acc3e870</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q9 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>Run this same path 5 times and record the option order each time, then compare them.
-1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician
-10. Q6 = Primary-care physician
-11. Q7 = Very poor
-12. Q8 = 0</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>At Q9, fill in every row, then submit.</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>1. the order the options appear in at Q9 is NOT identical on every run</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>Shuffled options</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Q10 | Did you contact support during the experience? | single | Yes; No | Always show</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>TC-a8e061598c</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey flows correctly at Q10: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -4910,58 +4787,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>1. Q10 IS shown on the page
 2. the next question shown is Q11_SQ001</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Q10 | Did you contact support during the experience? | single | Yes; No | Always show</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>TC-de9a196b0a</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>Prove Q10 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -4978,59 +4855,59 @@
 13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>At Q10, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q10</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Q11 | Which support channels did you use? | multi | Phone; Email; Chat; In person; Self-service | Show if: Q10 == 'Yes'
 Validate: {"min_selections": 1}</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>TC-b3bf3cd967</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q11: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5062,59 +4939,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>1. Q11 IS shown on the page
 2. the next question shown is Q12</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Q11 | Which support channels did you use? | multi | Phone; Email; Chat; In person; Self-service | Show if: Q10 == 'Yes'
 Validate: {"min_selections": 1}</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>TC-27856e547a</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>Prove Q11 DOES appear when its condition is met. The QRE says show it if: Q10 == 'Yes'</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5132,58 +5009,58 @@
 14. Q10 = Yes</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>At Q11, tick 1 option (Phone), then submit.</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>1. Q11 IS shown on the page</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Q11 | Which support channels did you use? | multi | Phone; Email; Chat; In person; Self-service | Show if: Q10 == 'Yes'
 Validate: {"min_selections": 1}</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>TC-56f140e989</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Prove Q11 does NOT appear when its condition is not met. The QRE says show it if: Q10 == 'Yes'</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5201,59 +5078,59 @@
 14. Q10 = No</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>After submitting Q10, look for Q11 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>1. Q11 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>Q11 | Which support channels did you use? | multi | Phone; Email; Chat; In person; Self-service | Show if: Q10 == 'Yes'
 Validate: {"min_selections": 1}</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>TC-4384054146</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>Prove Q11 ACCEPTS an answer that obeys its rule. The QRE's rule is: at least 1 option must be selected</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5271,58 +5148,58 @@
 14. Q10 = Yes</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>At Q11, tick 1 option (Phone), then submit.</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Q11 | Which support channels did you use? | multi | Phone; Email; Chat; In person; Self-service | Show if: Q10 == 'Yes'
 Validate: {"min_selections": 1}</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>TC-eb14baebac</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Prove Q11 REJECTS an answer that breaks its rule. The QRE's rule is: at least 1 option must be selected</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5340,59 +5217,59 @@
 14. Q10 = Yes</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q11</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>Q11 | Which support channels did you use? | multi | Phone; Email; Chat; In person; Self-service | Show if: Q10 == 'Yes'
 Validate: {"min_selections": 1}</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>TC-dffc167ba8</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>Prove Q11 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question  [Same actions as TC-eb14baebac on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5410,58 +5287,58 @@
 14. Q10 = Yes</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q11</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>Q12 | Was your issue resolved? | single | Fully; Partly; Not resolved | Show if: Q10 == 'Yes'</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>TC-5f091ba7d4</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q12: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5493,58 +5370,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>1. Q12 IS shown on the page
 2. the next question shown is Q13</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>Q12 | Was your issue resolved? | single | Fully; Partly; Not resolved | Show if: Q10 == 'Yes'</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>TC-c738ab6a74</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>Prove Q12 DOES appear when its condition is met. The QRE says show it if: Q10 == 'Yes'</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5563,57 +5440,57 @@
 15. Q11 = Phone</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>At Q12, choose “Fully”, then submit.</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>1. Q12 IS shown on the page</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Q12 | Was your issue resolved? | single | Fully; Partly; Not resolved | Show if: Q10 == 'Yes'</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>TC-9a14bc6add</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>Prove Q12 does NOT appear when its condition is not met. The QRE says show it if: Q10 == 'Yes'</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5631,58 +5508,58 @@
 14. Q10 = No</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>After submitting Q10, look for Q12 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>1. Q12 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Q12 | Was your issue resolved? | single | Fully; Partly; Not resolved | Show if: Q10 == 'Yes'</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>TC-1a48ee29c4</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>Prove Q12 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5701,58 +5578,58 @@
 15. Q11 = Phone</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>At Q12, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q12</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Q13 | How much effort did resolution require? | single | 1 - Very low; 2; 3; 4; 5 - Very high | Show if: Q12 in ['Fully','Partly']</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>TC-2467510b13</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q13: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5784,58 +5661,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>1. Q13 IS shown on the page
 2. the next question shown is Q15</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Q13 | How much effort did resolution require? | single | 1 - Very low; 2; 3; 4; 5 - Very high | Show if: Q12 in ['Fully','Partly']</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>TC-14fc8e54da</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>Prove Q13 DOES appear when its condition is met. The QRE says show it if: Q12 in ['Fully','Partly']</t>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5855,57 +5732,57 @@
 16. Q12 = Fully</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>At Q13, choose “Very low”, then submit.</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
         <is>
           <t>1. Q13 IS shown on the page</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Q13 | How much effort did resolution require? | single | 1 - Very low; 2; 3; 4; 5 - Very high | Show if: Q12 in ['Fully','Partly']</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>TC-f2b230b48d</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>Prove Q13 does NOT appear when its condition is not met. The QRE says show it if: Q12 in ['Fully','Partly']</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5925,58 +5802,58 @@
 16. Q12 = Not resolved</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>After submitting Q12, look for Q13 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>1. Q13 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>Q13 | How much effort did resolution require? | single | 1 - Very low; 2; 3; 4; 5 - Very high | Show if: Q12 in ['Fully','Partly']</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>TC-b4b5e1d353</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>Prove Q13 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G82" s="3" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -5996,59 +5873,59 @@
 16. Q12 = Fully</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>At Q13, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I82" s="3" t="inlineStr">
+      <c r="I80" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q13</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>TC-694ad669e7</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q14: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6080,59 +5957,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="I81" s="3" t="inlineStr">
         <is>
           <t>1. Q14 IS shown on the page
 2. the next question shown is Q15</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>TC-cdc8f528b6</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 DOES appear when its condition is met. The QRE says show it if: Q12 == 'Not resolved'</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6152,58 +6029,58 @@
 16. Q12 = Not resolved</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>At Q14, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
-      <c r="I84" s="3" t="inlineStr">
+      <c r="I82" s="3" t="inlineStr">
         <is>
           <t>1. Q14 IS shown on the page</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>TC-b87037f64b</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 does NOT appear when its condition is not met. The QRE says show it if: Q12 == 'Not resolved'</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6224,59 +6101,59 @@
 17. Q13 = Very low</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>After submitting Q13, look for Q14 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
         <is>
           <t>1. Q14 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>TC-0da0e99f10</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6296,58 +6173,58 @@
 16. Q12 = Not resolved</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t>At Q14, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
-      <c r="I86" s="3" t="inlineStr">
+      <c r="I84" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>TC-b12c5c54f5</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G87" s="3" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6367,59 +6244,59 @@
 16. Q12 = Not resolved</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>At Q14, type a 501-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q14</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>TC-c5e322dbf1</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6439,59 +6316,59 @@
 16. Q12 = Not resolved</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H86" s="3" t="inlineStr">
         <is>
           <t>At Q14, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I86" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q14</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>TC-4885664620</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6511,58 +6388,58 @@
 16. Q12 = Not resolved</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>At Q14, type a 500-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I89" s="3" t="inlineStr">
+      <c r="I87" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>TC-39c3f76ab7</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 10 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6582,58 +6459,58 @@
 16. Q12 = Not resolved</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="I88" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Q14 | Why was the issue not resolved? | text | — | Show if: Q12 == 'Not resolved'
 Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>TC-05fb791e04</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G91" s="3" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6653,58 +6530,58 @@
 16. Q12 = Not resolved</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>At Q14, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
-      <c r="I91" s="3" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q14</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Q15 | Have you considered switching providers? | single | Yes; No | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>TC-5b4bc2d018</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q15: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6736,58 +6613,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I92" s="3" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>1. Q15 IS shown on the page
 2. the next question shown is Q16</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>Q15 | Have you considered switching providers? | single | Yes; No | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>TC-fed888de92</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>Prove Q15 DOES appear when its condition is met. The QRE says show it if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6808,57 +6685,57 @@
 17. Q13 = Very low</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>At Q15, choose “Yes”, then submit.</t>
         </is>
       </c>
-      <c r="I93" s="3" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>1. Q15 IS shown on the page</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>Q15 | Have you considered switching providers? | single | Yes; No | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>TC-08990139ce</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>Prove Q15 does NOT appear when its condition is not met. The QRE says show it if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6876,58 +6753,58 @@
 14. Q13 = Very low</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H92" s="3" t="inlineStr">
         <is>
           <t>After submitting Q13, look for Q15 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I92" s="3" t="inlineStr">
         <is>
           <t>1. Q15 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Q15</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>Q15 | Have you considered switching providers? | single | Yes; No | Show if: Q3 != 'None/currently not using'</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>TC-ca68eda86a</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>Prove Q15 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G95" s="3" t="inlineStr">
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -6948,59 +6825,59 @@
 17. Q13 = Very low</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>At Q15, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I95" s="3" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q15</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>TC-21c743eb6a</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q16: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7032,59 +6909,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="H94" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I96" s="3" t="inlineStr">
+      <c r="I94" s="3" t="inlineStr">
         <is>
           <t>1. Q16 IS shown on the page
 2. the next question shown is Q18_SQ001</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J94" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>TC-2111ecce2f</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 DOES appear when its condition is met. The QRE says show it if: Q15 == 'Yes'</t>
         </is>
       </c>
-      <c r="G97" s="3" t="inlineStr">
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7106,58 +6983,58 @@
 18. Q15 = Yes</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="H95" s="3" t="inlineStr">
         <is>
           <t>At Q16, choose “Price”, then submit.</t>
         </is>
       </c>
-      <c r="I97" s="3" t="inlineStr">
+      <c r="I95" s="3" t="inlineStr">
         <is>
           <t>1. Q16 IS shown on the page</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>TC-e5efe2e244</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 does NOT appear when its condition is not met. The QRE says show it if: Q15 == 'Yes'</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7179,59 +7056,59 @@
 18. Q15 = No</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
         <is>
           <t>After submitting Q15, look for Q16 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="I96" s="3" t="inlineStr">
         <is>
           <t>1. Q16 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>TC-1ba7a2b2f4</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G99" s="3" t="inlineStr">
+      <c r="G97" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7253,59 +7130,59 @@
 18. Q15 = Yes</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
+      <c r="H97" s="3" t="inlineStr">
         <is>
           <t>At Q16, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I99" s="3" t="inlineStr">
+      <c r="I97" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q16</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>TC-99ecbaf9d7</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 still shows all 6 of its options when shuffled, with none dropped and none duplicated</t>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr">
+      <c r="G98" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7327,59 +7204,59 @@
 18. Q15 = Yes</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="H98" s="3" t="inlineStr">
         <is>
           <t>At Q16, choose “Price”, then submit.</t>
         </is>
       </c>
-      <c r="I100" s="3" t="inlineStr">
+      <c r="I98" s="3" t="inlineStr">
         <is>
           <t>1. Q16 shows exactly 6 options, none missing and none repeated
 2. the options shown at Q16 are exactly: Competitor offer, Features, Other, Poor support, Price, Service quality</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Q16</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>Q16 | What is the main reason for considering a switch? | single | Price; Service quality; Features; Poor support; Competitor offer; Other | Show if: Q15 == 'Yes'
 Randomize</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>TC-e519b16991</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>Prove Q16 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>Run this same path 5 times and record the option order each time, then compare them.
 1. S1 = Yes
@@ -7402,58 +7279,58 @@
 18. Q15 = Yes</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
+      <c r="H99" s="3" t="inlineStr">
         <is>
           <t>At Q16, choose “Price”, then submit.</t>
         </is>
       </c>
-      <c r="I101" s="3" t="inlineStr">
+      <c r="I99" s="3" t="inlineStr">
         <is>
           <t>1. the order the options appear in at Q16 is NOT identical on every run</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>TC-7d65461215</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q17: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7486,59 +7363,59 @@
 29. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I100" s="3" t="inlineStr">
         <is>
           <t>1. Q17 IS shown on the page
 2. the next question shown is Q18_SQ001</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>TC-ba1e176a44</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 DOES appear when its condition is met. The QRE says show it if: Q16 == 'Other'</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7561,58 +7438,58 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
+      <c r="H101" s="3" t="inlineStr">
         <is>
           <t>At Q17, type “xxx”, then submit.</t>
         </is>
       </c>
-      <c r="I103" s="3" t="inlineStr">
+      <c r="I101" s="3" t="inlineStr">
         <is>
           <t>1. Q17 IS shown on the page</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>TC-220d2848e3</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 does NOT appear when its condition is not met. The QRE says show it if: Q16 == 'Other'</t>
         </is>
       </c>
-      <c r="G104" s="3" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7635,59 +7512,59 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>After submitting Q16, look for Q17 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I104" s="3" t="inlineStr">
+      <c r="I102" s="3" t="inlineStr">
         <is>
           <t>1. Q17 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J102" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>TC-125b3c2534</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at least 3 characters; the answer must be at most 200 characters</t>
         </is>
       </c>
-      <c r="G105" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7710,58 +7587,58 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>At Q17, type “xxx”, then submit.</t>
         </is>
       </c>
-      <c r="I105" s="3" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>TC-8b10a27e5b</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 3 characters; the answer must be at most 200 characters</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7784,59 +7661,59 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
+      <c r="H104" s="3" t="inlineStr">
         <is>
           <t>At Q17, type a 201-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I106" s="3" t="inlineStr">
+      <c r="I104" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q17</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>TC-0b9a7cfabb</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr">
+      <c r="G105" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7859,59 +7736,59 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
+      <c r="H105" s="3" t="inlineStr">
         <is>
           <t>At Q17, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I107" s="3" t="inlineStr">
+      <c r="I105" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q17</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>TC-c3e04e6d69</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 3 characters; the answer must be at most 200 characters</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
+      <c r="G106" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -7934,58 +7811,58 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
+      <c r="H106" s="3" t="inlineStr">
         <is>
           <t>At Q17, type a 200-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I108" s="3" t="inlineStr">
+      <c r="I106" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>TC-62010da48b</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 3 characters; the answer must be at most 200 characters</t>
         </is>
       </c>
-      <c r="G109" s="3" t="inlineStr">
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8008,58 +7885,58 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
+      <c r="H107" s="3" t="inlineStr">
         <is>
           <t>At Q17, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
-      <c r="I109" s="3" t="inlineStr">
+      <c r="I107" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Q17</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>Q17 | Please specify the other switching reason. | text | — | Show if: Q16 == 'Other'
 Validate: {"min_length": 3, "max_length": 200}</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>TC-e9d75526e2</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>Prove Q17 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G110" s="3" t="inlineStr">
+      <c r="G108" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8082,58 +7959,58 @@
 19. Q16 = Other</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H108" s="3" t="inlineStr">
         <is>
           <t>At Q17, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
-      <c r="I110" s="3" t="inlineStr">
+      <c r="I108" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q17</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>TC-10edffc232</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q18: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G111" s="3" t="inlineStr">
+      <c r="G109" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8165,58 +8042,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
+      <c r="H109" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I111" s="3" t="inlineStr">
+      <c r="I109" s="3" t="inlineStr">
         <is>
           <t>1. Q18 IS shown on the page
 2. the next question shown is Q19</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>TC-10f288c00b</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>Prove Q18 ACCEPTS an answer that obeys its rule. The QRE's rule is: the numbers entered must add up to exactly 100</t>
         </is>
       </c>
-      <c r="G112" s="3" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8239,57 +8116,57 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="H110" s="3" t="inlineStr">
         <is>
           <t>At Q18, fill in every row, then submit.</t>
         </is>
       </c>
-      <c r="I112" s="3" t="inlineStr">
+      <c r="I110" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>TC-e0b1d06bf4</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>Prove reject rule R18 does NOT fire. The rule is: sum(Q18) != 100  [Same actions as TC-10f288c00b on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8312,57 +8189,57 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>At Q18, fill in every row, then submit.</t>
         </is>
       </c>
-      <c r="I113" s="3" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>TC-59337d0674</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>Prove Q18 REJECTS an answer that breaks its rule. The QRE's rule is: the numbers entered must add up to exactly 100</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G112" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8385,58 +8262,58 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H112" s="3" t="inlineStr">
         <is>
           <t>At Q18, fill in every row, then submit.</t>
         </is>
       </c>
-      <c r="I114" s="3" t="inlineStr">
+      <c r="I112" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q18</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>TC-03fd09a67c</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>Prove reject rule R18 DOES fire. The rule is: sum(Q18) != 100</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr">
+      <c r="G113" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8459,58 +8336,58 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
+      <c r="H113" s="3" t="inlineStr">
         <is>
           <t>At Q18, fill in every row, then submit.</t>
         </is>
       </c>
-      <c r="I115" s="3" t="inlineStr">
+      <c r="I113" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against R18</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr">
+      <c r="J113" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>Q18 | Allocate 100 points across the factors that drive your decision. | constant_sum | Price; Quality; Convenience; Trust; Support | Validate: {"sum": 100}</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>TC-1ef93dc899</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>Prove Q18 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a constant_sum question</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
+      <c r="G114" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8533,59 +8410,59 @@
 19. Q16 = Price</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="H114" s="3" t="inlineStr">
         <is>
           <t>At Q18, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I116" s="3" t="inlineStr">
+      <c r="I114" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q18</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J114" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>Q19 | Which new proposition do you prefer? | single | Concept A; Concept B; Concept C | Randomize
 Concept descriptions are displayed in randomized order; store display order.</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>TC-88093bffe3</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q19: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
+      <c r="G115" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8617,59 +8494,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
+      <c r="H115" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr">
+      <c r="I115" s="3" t="inlineStr">
         <is>
           <t>1. Q19 IS shown on the page
 2. the next question shown is Q20</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J115" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>Q19 | Which new proposition do you prefer? | single | Concept A; Concept B; Concept C | Randomize
 Concept descriptions are displayed in randomized order; store display order.</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>TC-60b738ceb3</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>Prove Q19 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G118" s="3" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8693,59 +8570,59 @@
 20. Q18 = Price=20; Quality=20; Convenience=20...</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="H116" s="3" t="inlineStr">
         <is>
           <t>At Q19, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I118" s="3" t="inlineStr">
+      <c r="I116" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q19</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="J116" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>Q19 | Which new proposition do you prefer? | single | Concept A; Concept B; Concept C | Randomize
 Concept descriptions are displayed in randomized order; store display order.</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>TC-7c2129fe6f</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>Prove Q19 still shows all 3 of its options when shuffled, with none dropped and none duplicated</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8769,59 +8646,59 @@
 20. Q18 = Price=20; Quality=20; Convenience=20...</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="H117" s="3" t="inlineStr">
         <is>
           <t>At Q19, choose “Concept A”, then submit.</t>
         </is>
       </c>
-      <c r="I119" s="3" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr">
         <is>
           <t>1. Q19 shows exactly 3 options, none missing and none repeated
 2. the options shown at Q19 are exactly: Concept A, Concept B, Concept C</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="J117" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>Q19 | Which new proposition do you prefer? | single | Concept A; Concept B; Concept C | Randomize
 Concept descriptions are displayed in randomized order; store display order.</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>TC-6789ff4e74</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>Prove Q19 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>Run this same path 5 times and record the option order each time, then compare them.
 1. S1 = Yes
@@ -8846,57 +8723,57 @@
 20. Q18 = Price=20; Quality=20; Convenience=20...</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="H118" s="3" t="inlineStr">
         <is>
           <t>At Q19, choose “Concept A”, then submit.</t>
         </is>
       </c>
-      <c r="I120" s="3" t="inlineStr">
+      <c r="I118" s="3" t="inlineStr">
         <is>
           <t>1. the order the options appear in at Q19 is NOT identical on every run</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="J118" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>Q20 | How appealing is the selected proposition? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>TC-a892eef1e4</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q20: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -8928,58 +8805,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
+      <c r="H119" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I121" s="3" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr">
         <is>
           <t>1. Q20 IS shown on the page
 2. the next question shown is Q21</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>Q20 | How appealing is the selected proposition? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>TC-a90db4cc87</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>Prove Q20 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G120" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9004,58 +8881,58 @@
 21. Q19 = Concept A</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H120" s="3" t="inlineStr">
         <is>
           <t>At Q20, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="I120" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q20</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="J120" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>Q20 | How appealing is the selected proposition? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>TC-cc22176bcb</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>Q20's wording comes from Q19's answer: the earlier answer should appear in the wording</t>
         </is>
       </c>
-      <c r="G123" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9080,57 +8957,57 @@
 21. Q19 = Concept A</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
+      <c r="H121" s="3" t="inlineStr">
         <is>
           <t>At Q20, choose “Very poor”, then submit.</t>
         </is>
       </c>
-      <c r="I123" s="3" t="inlineStr">
+      <c r="I121" s="3" t="inlineStr">
         <is>
           <t>1. Q20's wording includes the words: Concept A</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr">
         <is>
           <t>Wording carried forward</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>TC-5b2db56449</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q21: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9162,58 +9039,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="H122" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I124" s="3" t="inlineStr">
+      <c r="I122" s="3" t="inlineStr">
         <is>
           <t>1. Q21 IS shown on the page
 2. the next question shown is D1</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>TC-a8fcf8afbe</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>Prove Q21 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G125" s="3" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9239,57 +9116,57 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H125" s="3" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>At Q21, type “xxxxx”, then submit.</t>
         </is>
       </c>
-      <c r="I125" s="3" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="J123" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>TC-5c326b3c25</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>Prove Q21 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G126" s="3" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9315,58 +9192,58 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
+      <c r="H124" s="3" t="inlineStr">
         <is>
           <t>At Q21, type a 501-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I126" s="3" t="inlineStr">
+      <c r="I124" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q21</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>TC-a59227b46e</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>Prove Q21 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr">
+      <c r="G125" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9392,58 +9269,58 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
+      <c r="H125" s="3" t="inlineStr">
         <is>
           <t>At Q21, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I127" s="3" t="inlineStr">
+      <c r="I125" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q21</t>
         </is>
       </c>
-      <c r="J127" s="2" t="inlineStr">
+      <c r="J125" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>TC-42363fd1b9</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>Q21's wording comes from Q19's answer: the earlier answer should appear in the wording</t>
         </is>
       </c>
-      <c r="G128" s="3" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9469,57 +9346,57 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
+      <c r="H126" s="3" t="inlineStr">
         <is>
           <t>At Q21, type “xxxxx”, then submit.</t>
         </is>
       </c>
-      <c r="I128" s="3" t="inlineStr">
+      <c r="I126" s="3" t="inlineStr">
         <is>
           <t>1. Q21's wording includes the words: Concept A</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr">
+      <c r="J126" s="2" t="inlineStr">
         <is>
           <t>Wording carried forward</t>
         </is>
       </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>TC-524d7f1984</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>Prove Q21 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G129" s="3" t="inlineStr">
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9545,57 +9422,57 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>At Q21, type a 500-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I129" s="3" t="inlineStr">
+      <c r="I127" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>TC-8aaf18bb07</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
         <is>
           <t>Prove Q21 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
-      <c r="G130" s="3" t="inlineStr">
+      <c r="G128" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9621,57 +9498,57 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
+      <c r="H128" s="3" t="inlineStr">
         <is>
           <t>At Q21, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
-      <c r="I130" s="3" t="inlineStr">
+      <c r="I128" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="J128" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Q21</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>TC-2b316ac481</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>Prove Q21 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G131" s="3" t="inlineStr">
+      <c r="G129" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9697,58 +9574,58 @@
 22. Q20 = Very poor</t>
         </is>
       </c>
-      <c r="H131" s="3" t="inlineStr">
+      <c r="H129" s="3" t="inlineStr">
         <is>
           <t>At Q21, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
-      <c r="I131" s="3" t="inlineStr">
+      <c r="I129" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q21</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="J129" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>TC-9d345eef73</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D1: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G132" s="3" t="inlineStr">
+      <c r="G130" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9780,58 +9657,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
+      <c r="H130" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I132" s="3" t="inlineStr">
+      <c r="I130" s="3" t="inlineStr">
         <is>
           <t>1. D1 IS shown on the page
 2. the next question shown is D2</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>TC-eba66f169b</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G133" s="3" t="inlineStr">
+      <c r="G131" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9858,58 +9735,58 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="H131" s="3" t="inlineStr">
         <is>
           <t>At D1, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr">
+      <c r="I131" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D1</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="J131" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>TC-640f339984</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'North' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G134" s="3" t="inlineStr">
+      <c r="G132" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9936,57 +9813,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H132" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="I132" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>TC-6a4f70dee1</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'South' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10013,57 +9890,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="H133" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
-      <c r="I135" s="3" t="inlineStr">
+      <c r="I133" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>TC-add22f59a7</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'East' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10090,57 +9967,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr">
+      <c r="I134" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>TC-e3f1efd2fe</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'West' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10167,57 +10044,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
-      <c r="I137" s="3" t="inlineStr">
+      <c r="I135" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>TC-faf234994c</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'Central' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G138" s="3" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10244,57 +10121,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
+      <c r="H136" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
-      <c r="I138" s="3" t="inlineStr">
+      <c r="I136" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>TC-a1ac064e4d</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10326,58 +10203,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="H137" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr">
+      <c r="I137" s="3" t="inlineStr">
         <is>
           <t>1. D2 IS shown on the page
 2. the next question shown is D3</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>TC-e3d95ddd0a</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10405,58 +10282,58 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>At D2, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I140" s="3" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D2</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>TC-9e12b71968</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '21-29' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10484,57 +10361,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
+      <c r="H139" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “21-29”, then submit.</t>
         </is>
       </c>
-      <c r="I141" s="3" t="inlineStr">
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>TC-6c5662fab4</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '30-39' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10562,57 +10439,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “30-39”, then submit.</t>
         </is>
       </c>
-      <c r="I142" s="3" t="inlineStr">
+      <c r="I140" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>TC-dd41da385a</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '40-49' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G143" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10640,57 +10517,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “40-49”, then submit.</t>
         </is>
       </c>
-      <c r="I143" s="3" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>TC-d79d3aefa5</t>
         </is>
       </c>
-      <c r="F144" s="3" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '50-59' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G144" s="3" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10718,57 +10595,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “50-59”, then submit.</t>
         </is>
       </c>
-      <c r="I144" s="3" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>TC-718cbe9fd7</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '60+' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G145" s="3" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10796,57 +10673,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
+      <c r="H143" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “60+”, then submit.</t>
         </is>
       </c>
-      <c r="I145" s="3" t="inlineStr">
+      <c r="I143" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>D3 | How do you describe your gender? | single | Woman; Man; Non-binary; Prefer to self-describe; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>TC-531a6544ed</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D3: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr">
+      <c r="G144" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10878,58 +10755,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
+      <c r="H144" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I146" s="3" t="inlineStr">
+      <c r="I144" s="3" t="inlineStr">
         <is>
           <t>1. D3 IS shown on the page
 2. the next question shown is D4</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>D3 | How do you describe your gender? | single | Woman; Man; Non-binary; Prefer to self-describe; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>TC-799f9fd202</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>Prove D3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G147" s="3" t="inlineStr">
+      <c r="G145" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10958,58 +10835,58 @@
 25. D2 = 21-29</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
         <is>
           <t>At D3, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I147" s="3" t="inlineStr">
+      <c r="I145" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D3</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>D4 | What is your household or organizational decision band? | single | Band 1; Band 2; Band 3; Band 4; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>TC-0c2ebe3557</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D4: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G148" s="3" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11041,58 +10918,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I148" s="3" t="inlineStr">
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>1. D4 IS shown on the page
 2. the next question shown is Q22</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>D4 | What is your household or organizational decision band? | single | Band 1; Band 2; Band 3; Band 4; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>TC-6408b44286</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>Prove D4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr">
+      <c r="G147" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11122,58 +10999,58 @@
 26. D3 = Woman</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
+      <c r="H147" s="3" t="inlineStr">
         <is>
           <t>At D4, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I149" s="3" t="inlineStr">
+      <c r="I147" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D4</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Q22</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t>Q22 | May we use your anonymized comments in internal reporting? | single | Yes; No | Always show</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>TC-d3a3106833</t>
         </is>
       </c>
-      <c r="F150" s="3" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q22: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G150" s="3" t="inlineStr">
+      <c r="G148" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11205,58 +11082,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
+      <c r="H148" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I150" s="3" t="inlineStr">
+      <c r="I148" s="3" t="inlineStr">
         <is>
           <t>1. Q22 IS shown on the page
 2. the next question shown is Q23</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Q22</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>Q22 | May we use your anonymized comments in internal reporting? | single | Yes; No | Always show</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>TC-7596aff04a</t>
         </is>
       </c>
-      <c r="F151" s="3" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>Prove Q22 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G151" s="3" t="inlineStr">
+      <c r="G149" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11287,59 +11164,59 @@
 27. D4 = Band 1</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H149" s="3" t="inlineStr">
         <is>
           <t>At Q22, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I151" s="3" t="inlineStr">
+      <c r="I149" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q22</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>TC-66de0d40bf</t>
         </is>
       </c>
-      <c r="F152" s="3" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q23: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G152" s="3" t="inlineStr">
+      <c r="G150" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11371,59 +11248,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
+      <c r="H150" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I152" s="3" t="inlineStr">
+      <c r="I150" s="3" t="inlineStr">
         <is>
           <t>1. Q23 IS shown on the page
 2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>TC-27239f8502</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G153" s="3" t="inlineStr">
+      <c r="G151" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11455,58 +11332,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="H151" s="3" t="inlineStr">
         <is>
           <t>At Q23, type “x”, then submit.</t>
         </is>
       </c>
-      <c r="I153" s="3" t="inlineStr">
+      <c r="I151" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C152" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>TC-de6bfa278d</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G154" s="3" t="inlineStr">
+      <c r="G152" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11538,59 +11415,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
+      <c r="H152" s="3" t="inlineStr">
         <is>
           <t>At Q23, type a 1001-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I154" s="3" t="inlineStr">
+      <c r="I152" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q23</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>TC-501913f6da</t>
         </is>
       </c>
-      <c r="F155" s="3" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 lets the respondent through with no answer, because the questionnaire marks it optional</t>
         </is>
       </c>
-      <c r="G155" s="3" t="inlineStr">
+      <c r="G153" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11622,58 +11499,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
+      <c r="H153" s="3" t="inlineStr">
         <is>
           <t>At Q23, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I155" s="3" t="inlineStr">
+      <c r="I153" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>TC-e8a2b0563a</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G156" s="3" t="inlineStr">
+      <c r="G154" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11705,58 +11582,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
+      <c r="H154" s="3" t="inlineStr">
         <is>
           <t>At Q23, type a 1000-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I156" s="3" t="inlineStr">
+      <c r="I154" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>TC-40e56a8b6b</t>
         </is>
       </c>
-      <c r="F157" s="3" t="inlineStr">
+      <c r="F155" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G157" s="3" t="inlineStr">
+      <c r="G155" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11788,58 +11665,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
+      <c r="H155" s="3" t="inlineStr">
         <is>
           <t>At Q23, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
-      <c r="I157" s="3" t="inlineStr">
+      <c r="I155" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>TC-38d0f2db08</t>
         </is>
       </c>
-      <c r="F158" s="3" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G158" s="3" t="inlineStr">
+      <c r="G156" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11871,53 +11748,53 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
+      <c r="H156" s="3" t="inlineStr">
         <is>
           <t>At Q23, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
-      <c r="I158" s="3" t="inlineStr">
+      <c r="I156" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>whole survey</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr"/>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr"/>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>TC-236280087d</t>
         </is>
       </c>
-      <c r="F159" s="3" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>Prove the survey finishes normally for a respondent who answers everything and triggers no screen-out</t>
         </is>
       </c>
-      <c r="G159" s="3" t="inlineStr">
+      <c r="G157" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11949,22 +11826,22 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
+      <c r="H157" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I159" s="3" t="inlineStr">
+      <c r="I157" s="3" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>Survey ends in the right place</t>
         </is>
       </c>
-      <c r="K159" s="2" t="inlineStr">
+      <c r="K157" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/out/C01_chronic_care_patient_journey/agent3/agent3_test_cases_for_review.xlsx
+++ b/out/C01_chronic_care_patient_journey/agent3/agent3_test_cases_for_review.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>TC-42363fd1b9</t>
+          <t>TC-524d7f1984</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Q21's wording comes from Q19's answer: the earlier answer should appear in the wording</t>
+          <t>Prove Q21 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -9561,17 +9561,17 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>At Q21, type “xxxxx”, then submit.</t>
+          <t>At Q21, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>1. Q21's wording includes the words: Concept A</t>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>Wording carried forward</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>TC-524d7f1984</t>
+          <t>TC-8aaf18bb07</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>At Q21, type a 500-character answer, then submit.</t>
+          <t>At Q21, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>TC-8aaf18bb07</t>
+          <t>TC-2b316ac481</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Prove Q21 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at least 5 characters; the answer must be at most 500 characters</t>
+          <t>Prove Q21 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -9713,17 +9713,18 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>At Q21, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+          <t>At Q21, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q21</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Answer rule accepts or rejects</t>
+          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -9738,12 +9739,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>DT3</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
+          <t>DT3 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -9753,92 +9754,15 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>TC-2b316ac481</t>
+          <t>TC-60f46acb6d</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Prove Q21 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
+          <t>Prove the survey flows correctly at DT3: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Personally manage an ongoing chronic health condition
-3. S3 = No
-4. S4 = No
-5. Q1 = Care Network A
-6. Q2 = Care Network A
-7. Q3 = Care Network A
-8. Q4 = Recently diagnosed
-9. Q5 = Primary-care physician
-10. Q6 = Primary-care physician
-11. Q7 = Very poor
-12. Q8 = 0
-13. Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor...
-14. Q10 = Yes
-15. Q11 = Phone
-16. Q12 = Fully
-17. Q13 = Very low
-18. Q15 = Yes
-19. Q16 = Price
-20. Q18 = Price=20; Quality=20; Convenience=20...
-21. Q19 = Concept A
-22. Q20 = Very poor</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>At Q21, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="I132" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q21</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>Blank answer is blocked</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>DT3</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>DT3 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>TC-60f46acb6d</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey flows correctly at DT3: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9870,57 +9794,57 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="H132" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr">
+      <c r="I132" s="3" t="inlineStr">
         <is>
           <t>1. the next question shown is D1</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>TC-9d345eef73</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D1: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G134" s="3" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -9952,58 +9876,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H133" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="I133" s="3" t="inlineStr">
         <is>
           <t>1. D1 IS shown on the page
 2. the next question shown is D2</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>TC-eba66f169b</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10030,58 +9954,58 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr">
         <is>
           <t>At D1, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I135" s="3" t="inlineStr">
+      <c r="I134" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D1</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>TC-640f339984</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'North' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10108,57 +10032,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr">
+      <c r="I135" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>TC-6a4f70dee1</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'South' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10185,57 +10109,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
+      <c r="H136" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
-      <c r="I137" s="3" t="inlineStr">
+      <c r="I136" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>TC-add22f59a7</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'East' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G138" s="3" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10262,57 +10186,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
+      <c r="H137" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
-      <c r="I138" s="3" t="inlineStr">
+      <c r="I137" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>TC-e3f1efd2fe</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'West' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10339,57 +10263,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>TC-faf234994c</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'Central' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10416,57 +10340,57 @@
 23. Q21 = xxxxx</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
+      <c r="H139" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
-      <c r="I140" s="3" t="inlineStr">
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>TC-a1ac064e4d</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10498,58 +10422,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I141" s="3" t="inlineStr">
+      <c r="I140" s="3" t="inlineStr">
         <is>
           <t>1. D2 IS shown on the page
 2. the next question shown is D3</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>TC-e3d95ddd0a</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10577,58 +10501,58 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>At D2, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I142" s="3" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D2</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>TC-9e12b71968</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '21-29' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G143" s="3" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10656,57 +10580,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “21-29”, then submit.</t>
         </is>
       </c>
-      <c r="I143" s="3" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>TC-6c5662fab4</t>
         </is>
       </c>
-      <c r="F144" s="3" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '30-39' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G144" s="3" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10734,57 +10658,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
+      <c r="H143" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “30-39”, then submit.</t>
         </is>
       </c>
-      <c r="I144" s="3" t="inlineStr">
+      <c r="I143" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>TC-dd41da385a</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '40-49' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G145" s="3" t="inlineStr">
+      <c r="G144" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10812,57 +10736,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
+      <c r="H144" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “40-49”, then submit.</t>
         </is>
       </c>
-      <c r="I145" s="3" t="inlineStr">
+      <c r="I144" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>TC-d79d3aefa5</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '50-59' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr">
+      <c r="G145" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10890,57 +10814,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “50-59”, then submit.</t>
         </is>
       </c>
-      <c r="I146" s="3" t="inlineStr">
+      <c r="I145" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>TC-718cbe9fd7</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_AGE lets a '60+' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G147" s="3" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -10968,57 +10892,57 @@
 24. D1 = North</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
         <is>
           <t>At D2, choose “60+”, then submit.</t>
         </is>
       </c>
-      <c r="I147" s="3" t="inlineStr">
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>D3 | How do you describe your gender? | single | Woman; Man; Non-binary; Prefer to self-describe; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>TC-531a6544ed</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D3: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G148" s="3" t="inlineStr">
+      <c r="G147" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11050,58 +10974,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
+      <c r="H147" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I148" s="3" t="inlineStr">
+      <c r="I147" s="3" t="inlineStr">
         <is>
           <t>1. D3 IS shown on the page
 2. the next question shown is D4</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t>D3 | How do you describe your gender? | single | Woman; Man; Non-binary; Prefer to self-describe; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>TC-799f9fd202</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr">
         <is>
           <t>Prove D3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr">
+      <c r="G148" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11130,58 +11054,58 @@
 25. D2 = 21-29</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
+      <c r="H148" s="3" t="inlineStr">
         <is>
           <t>At D3, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I149" s="3" t="inlineStr">
+      <c r="I148" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D3</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>D4 | What is your household or organizational decision band? | single | Band 1; Band 2; Band 3; Band 4; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>TC-0c2ebe3557</t>
         </is>
       </c>
-      <c r="F150" s="3" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D4: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G150" s="3" t="inlineStr">
+      <c r="G149" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11213,58 +11137,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
+      <c r="H149" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I150" s="3" t="inlineStr">
+      <c r="I149" s="3" t="inlineStr">
         <is>
           <t>1. D4 IS shown on the page
 2. the next question shown is Q22</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>D4 | What is your household or organizational decision band? | single | Band 1; Band 2; Band 3; Band 4; Prefer not to say | Always show</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>TC-6408b44286</t>
         </is>
       </c>
-      <c r="F151" s="3" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
         <is>
           <t>Prove D4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G151" s="3" t="inlineStr">
+      <c r="G150" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11294,58 +11218,58 @@
 26. D3 = Woman</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H150" s="3" t="inlineStr">
         <is>
           <t>At D4, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I151" s="3" t="inlineStr">
+      <c r="I150" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D4</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Q22</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>Q22 | May we use your anonymized comments in internal reporting? | single | Yes; No | Always show</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>TC-d3a3106833</t>
         </is>
       </c>
-      <c r="F152" s="3" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q22: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G152" s="3" t="inlineStr">
+      <c r="G151" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11377,58 +11301,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
+      <c r="H151" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I152" s="3" t="inlineStr">
+      <c r="I151" s="3" t="inlineStr">
         <is>
           <t>1. Q22 IS shown on the page
 2. the next question shown is Q23</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Q22</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C152" s="3" t="inlineStr">
         <is>
           <t>Q22 | May we use your anonymized comments in internal reporting? | single | Yes; No | Always show</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>TC-7596aff04a</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr">
         <is>
           <t>Prove Q22 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G153" s="3" t="inlineStr">
+      <c r="G152" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11459,59 +11383,59 @@
 27. D4 = Band 1</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="H152" s="3" t="inlineStr">
         <is>
           <t>At Q22, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I153" s="3" t="inlineStr">
+      <c r="I152" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q22</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>TC-66de0d40bf</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q23: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G154" s="3" t="inlineStr">
+      <c r="G153" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11543,59 +11467,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
+      <c r="H153" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I154" s="3" t="inlineStr">
+      <c r="I153" s="3" t="inlineStr">
         <is>
           <t>1. Q23 IS shown on the page
 2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>TC-27239f8502</t>
         </is>
       </c>
-      <c r="F155" s="3" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G155" s="3" t="inlineStr">
+      <c r="G154" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11627,58 +11551,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
+      <c r="H154" s="3" t="inlineStr">
         <is>
           <t>At Q23, type “x”, then submit.</t>
         </is>
       </c>
-      <c r="I155" s="3" t="inlineStr">
+      <c r="I154" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>TC-de6bfa278d</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr">
+      <c r="F155" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G156" s="3" t="inlineStr">
+      <c r="G155" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11710,59 +11634,59 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
+      <c r="H155" s="3" t="inlineStr">
         <is>
           <t>At Q23, type a 1001-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I156" s="3" t="inlineStr">
+      <c r="I155" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q23</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>TC-501913f6da</t>
         </is>
       </c>
-      <c r="F157" s="3" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 lets the respondent through with no answer, because the questionnaire marks it optional</t>
         </is>
       </c>
-      <c r="G157" s="3" t="inlineStr">
+      <c r="G156" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11794,58 +11718,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
+      <c r="H156" s="3" t="inlineStr">
         <is>
           <t>At Q23, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I157" s="3" t="inlineStr">
+      <c r="I156" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>TC-e8a2b0563a</t>
         </is>
       </c>
-      <c r="F158" s="3" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G158" s="3" t="inlineStr">
+      <c r="G157" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11877,58 +11801,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
+      <c r="H157" s="3" t="inlineStr">
         <is>
           <t>At Q23, type a 1000-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I158" s="3" t="inlineStr">
+      <c r="I157" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>TC-40e56a8b6b</t>
         </is>
       </c>
-      <c r="F159" s="3" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 1000 characters</t>
         </is>
       </c>
-      <c r="G159" s="3" t="inlineStr">
+      <c r="G158" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -11960,58 +11884,58 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
+      <c r="H158" s="3" t="inlineStr">
         <is>
           <t>At Q23, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
-      <c r="I159" s="3" t="inlineStr">
+      <c r="I158" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
 Optional</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>TC-38d0f2db08</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr">
         <is>
           <t>Prove Q23 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G160" s="3" t="inlineStr">
+      <c r="G159" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -12043,53 +11967,53 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
+      <c r="H159" s="3" t="inlineStr">
         <is>
           <t>At Q23, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
-      <c r="I160" s="3" t="inlineStr">
+      <c r="I159" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J160" s="2" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>whole survey</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr"/>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr"/>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>TC-236280087d</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
         <is>
           <t>Prove the survey finishes normally for a respondent who answers everything and triggers no screen-out</t>
         </is>
       </c>
-      <c r="G161" s="3" t="inlineStr">
+      <c r="G160" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Personally manage an ongoing chronic health condition
@@ -12121,22 +12045,22 @@
 28. Q22 = Yes</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
+      <c r="H160" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I161" s="3" t="inlineStr">
+      <c r="I160" s="3" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>Survey ends in the right place</t>
         </is>
       </c>
-      <c r="K161" s="2" t="inlineStr">
+      <c r="K160" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
